--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_3/262FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_3/262FL_10A.xlsx
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -8637,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -8654,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -8722,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -8756,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
